--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76177400</v>
+        <v>76177436</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R2" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76177446</v>
+        <v>76177438</v>
       </c>
       <c r="B3" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R3" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,12 +891,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -917,32 +907,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76177457</v>
+        <v>76177460</v>
       </c>
       <c r="B4" t="n">
-        <v>56075</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102116</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tobisgrissla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cepphus grylle</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,17 +935,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergsjöåsen , Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R4" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,12 +1007,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1033,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76175833</v>
+        <v>76177418</v>
       </c>
       <c r="B5" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,17 +1051,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergsjöåsen , Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R5" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2018-05-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2018-05-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,12 +1123,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1149,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76175877</v>
+        <v>76177447</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102987</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1194,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R6" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,22 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2018-05-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2018-05-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1239,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1270,50 +1255,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>76177459</v>
+        <v>76177380</v>
       </c>
       <c r="B7" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102976</v>
+        <v>102999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergsjöåsen , Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R7" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,12 +1355,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1386,50 +1371,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>76177388</v>
+        <v>76177446</v>
       </c>
       <c r="B8" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergsjöåsen , Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R8" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,12 +1471,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1502,15 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>76177438</v>
+        <v>76175877</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1547,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R9" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,22 +1557,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-05-13</t>
+          <t>2019-02-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-05-13</t>
+          <t>2019-02-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,12 +1587,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1623,15 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76177419</v>
+        <v>76177400</v>
       </c>
       <c r="B10" t="n">
-        <v>56366</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,34 +1614,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100136</v>
+        <v>103042</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergsjöåsen , Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R10" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,12 +1703,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1739,32 +1719,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76177393</v>
+        <v>76177402</v>
       </c>
       <c r="B11" t="n">
-        <v>56358</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100093</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjälluggla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bubo scandiacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1772,17 +1747,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergsjöåsen , Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567983.2476313366</v>
+        <v>567983</v>
       </c>
       <c r="R11" t="n">
-        <v>7082880.621889021</v>
+        <v>7082881</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,1412 +1819,15 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
+          <t>Stefan  Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>76175821</v>
-      </c>
-      <c r="B12" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>102964</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Fiskmås</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Larus canus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>76175838</v>
-      </c>
-      <c r="B13" t="n">
-        <v>56608</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>102981</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hussvala</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Delichon urbicum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>76177461</v>
-      </c>
-      <c r="B14" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>103008</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ärtsångare</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Curruca curruca</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>76175881</v>
-      </c>
-      <c r="B15" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>102952</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tofsvipa</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Vanellus vanellus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>76175862</v>
-      </c>
-      <c r="B16" t="n">
-        <v>55497</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>102106</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Skedand</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Spatula clypeata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>76177415</v>
-      </c>
-      <c r="B17" t="n">
-        <v>55729</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100044</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Kornknarr</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Crex crex</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>76177417</v>
-      </c>
-      <c r="B18" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>103035</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Kråka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Corvus corone</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>76177439</v>
-      </c>
-      <c r="B19" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>103037</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Stare</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Sturnus vulgaris</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>76177442</v>
-      </c>
-      <c r="B20" t="n">
-        <v>55834</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100091</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Storspov</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Numenius arquata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>76177380</v>
-      </c>
-      <c r="B21" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>102999</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Björktrast</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Turdus pilaris</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>76175839</v>
-      </c>
-      <c r="B22" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Fågelkalendern</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>76177379</v>
-      </c>
-      <c r="B23" t="n">
-        <v>56359</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100020</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Berguv</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Bubo bubo</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Bergsjöåsen , Ång</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>567983.2476313366</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7082880.621889021</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2018-05-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan  Magnusson </t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
         <is>
           <t>Fågelkalendern</t>
         </is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177438</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177418</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177447</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177380</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76175877</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177400</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,8 +1882,25 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>